--- a/HR Dataset.xlsx
+++ b/HR Dataset.xlsx
@@ -5,10 +5,10 @@
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Inception Python\project\Datahboard using excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Inception Python\project\HR-Dashboard-using-Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7632087-12BF-4716-BE0B-F2322435A0AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{559B9C6B-CB29-4381-9293-23B7C8DC1BD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
   <calcPr calcId="191029"/>
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId8"/>
-    <pivotCache cacheId="58" r:id="rId9"/>
+    <pivotCache cacheId="1" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -54,7 +54,7 @@
     </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{A2CB5862-8E78-49c6-8D9D-AF26E26ADB89}">
       <x15:timelineCachePivotCaches>
-        <pivotCache cacheId="16" r:id="rId15"/>
+        <pivotCache cacheId="2" r:id="rId15"/>
       </x15:timelineCachePivotCaches>
     </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}">
@@ -3033,6 +3033,52 @@
       <font>
         <b/>
         <i val="0"/>
+        <color rgb="FFFFC000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="24"/>
+        <color theme="1" tint="0.34998626667073579"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
         <sz val="26"/>
         <color rgb="FFFFC000"/>
       </font>
@@ -3077,35 +3123,6 @@
         <vertical/>
         <horizontal/>
       </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="20"/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1" tint="4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -3410,8 +3427,8 @@
   </dxfs>
   <tableStyles count="4" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Goat Slicer 2" pivot="0" table="0" count="10" xr9:uid="{E4F48D4C-BBDA-4F27-9EA6-321B0678CA49}">
-      <tableStyleElement type="wholeTable" dxfId="3"/>
-      <tableStyleElement type="headerRow" dxfId="2"/>
+      <tableStyleElement type="wholeTable" dxfId="1"/>
+      <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
     <tableStyle name="Goat Slicer 2 2" pivot="0" table="0" count="10" xr9:uid="{8F163650-529B-41EA-8A14-305E060B8C92}">
       <tableStyleElement type="wholeTable" dxfId="19"/>
@@ -3419,8 +3436,8 @@
     </tableStyle>
     <tableStyle name="Slicer Style 1" pivot="0" table="0" count="0" xr9:uid="{8FEAAA40-66B5-4731-95D1-3E2FE21399B7}"/>
     <tableStyle name="TimeSlicerStyleLight 3" pivot="0" table="0" count="9" xr9:uid="{99AAB8B0-2531-41E6-BD3D-62AE04BDB4F0}">
-      <tableStyleElement type="wholeTable" dxfId="1"/>
-      <tableStyleElement type="headerRow" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="3"/>
+      <tableStyleElement type="headerRow" dxfId="2"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -3430,7 +3447,463 @@
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{46F421CA-312F-682f-3DD2-61675219B42D}">
-      <x14:dxfs count="16">
+      <x14:dxfs count="40">
+        <dxf>
+          <font>
+            <color rgb="FF000000"/>
+          </font>
+          <fill>
+            <gradientFill degree="90">
+              <stop position="0">
+                <color rgb="FFF8E162"/>
+              </stop>
+              <stop position="1">
+                <color rgb="FFFCF7E0"/>
+              </stop>
+            </gradientFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FF999999"/>
+            </left>
+            <right style="thin">
+              <color rgb="FF999999"/>
+            </right>
+            <top style="thin">
+              <color rgb="FF999999"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FF999999"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF000000"/>
+          </font>
+          <fill>
+            <gradientFill degree="90">
+              <stop position="0">
+                <color rgb="FFF8E162"/>
+              </stop>
+              <stop position="1">
+                <color rgb="FFFCF7E0"/>
+              </stop>
+            </gradientFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FF999999"/>
+            </left>
+            <right style="thin">
+              <color rgb="FF999999"/>
+            </right>
+            <top style="thin">
+              <color rgb="FF999999"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FF999999"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF000000"/>
+          </font>
+          <fill>
+            <gradientFill degree="90">
+              <stop position="0">
+                <color rgb="FFF8E162"/>
+              </stop>
+              <stop position="1">
+                <color rgb="FFFCF7E0"/>
+              </stop>
+            </gradientFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FF999999"/>
+            </left>
+            <right style="thin">
+              <color rgb="FF999999"/>
+            </right>
+            <top style="thin">
+              <color rgb="FF999999"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FF999999"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF000000"/>
+          </font>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor auto="1"/>
+              <bgColor rgb="FFFFC000"/>
+            </patternFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FF999999"/>
+            </left>
+            <right style="thin">
+              <color rgb="FF999999"/>
+            </right>
+            <top style="thin">
+              <color rgb="FF999999"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FF999999"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF828282"/>
+          </font>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor theme="4" tint="0.79998168889431442"/>
+              <bgColor theme="4" tint="0.79998168889431442"/>
+            </patternFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FFCCCCCC"/>
+            </left>
+            <right style="thin">
+              <color rgb="FFCCCCCC"/>
+            </right>
+            <top style="thin">
+              <color rgb="FFCCCCCC"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FFCCCCCC"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF000000"/>
+          </font>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor theme="4" tint="0.59999389629810485"/>
+              <bgColor theme="4" tint="0.59999389629810485"/>
+            </patternFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FF999999"/>
+            </left>
+            <right style="thin">
+              <color rgb="FF999999"/>
+            </right>
+            <top style="thin">
+              <color rgb="FF999999"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FF999999"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF828282"/>
+          </font>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor rgb="FFFFFFFF"/>
+              <bgColor rgb="FFFFFFFF"/>
+            </patternFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FFE0E0E0"/>
+            </left>
+            <right style="thin">
+              <color rgb="FFE0E0E0"/>
+            </right>
+            <top style="thin">
+              <color rgb="FFE0E0E0"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FFE0E0E0"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF000000"/>
+          </font>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor rgb="FFFFFFFF"/>
+              <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+            </patternFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FFCCCCCC"/>
+            </left>
+            <right style="thin">
+              <color rgb="FFCCCCCC"/>
+            </right>
+            <top style="thin">
+              <color rgb="FFCCCCCC"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FFCCCCCC"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF000000"/>
+          </font>
+          <fill>
+            <gradientFill degree="90">
+              <stop position="0">
+                <color rgb="FFF8E162"/>
+              </stop>
+              <stop position="1">
+                <color rgb="FFFCF7E0"/>
+              </stop>
+            </gradientFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FF999999"/>
+            </left>
+            <right style="thin">
+              <color rgb="FF999999"/>
+            </right>
+            <top style="thin">
+              <color rgb="FF999999"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FF999999"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF000000"/>
+          </font>
+          <fill>
+            <gradientFill degree="90">
+              <stop position="0">
+                <color rgb="FFF8E162"/>
+              </stop>
+              <stop position="1">
+                <color rgb="FFFCF7E0"/>
+              </stop>
+            </gradientFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FF999999"/>
+            </left>
+            <right style="thin">
+              <color rgb="FF999999"/>
+            </right>
+            <top style="thin">
+              <color rgb="FF999999"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FF999999"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF000000"/>
+          </font>
+          <fill>
+            <gradientFill degree="90">
+              <stop position="0">
+                <color rgb="FFF8E162"/>
+              </stop>
+              <stop position="1">
+                <color rgb="FFFCF7E0"/>
+              </stop>
+            </gradientFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FF999999"/>
+            </left>
+            <right style="thin">
+              <color rgb="FF999999"/>
+            </right>
+            <top style="thin">
+              <color rgb="FF999999"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FF999999"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF000000"/>
+          </font>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor auto="1"/>
+              <bgColor rgb="FFFFC000"/>
+            </patternFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FF999999"/>
+            </left>
+            <right style="thin">
+              <color rgb="FF999999"/>
+            </right>
+            <top style="thin">
+              <color rgb="FF999999"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FF999999"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF828282"/>
+          </font>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor theme="4" tint="0.79998168889431442"/>
+              <bgColor theme="4" tint="0.79998168889431442"/>
+            </patternFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FFCCCCCC"/>
+            </left>
+            <right style="thin">
+              <color rgb="FFCCCCCC"/>
+            </right>
+            <top style="thin">
+              <color rgb="FFCCCCCC"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FFCCCCCC"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF000000"/>
+          </font>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor theme="4" tint="0.59999389629810485"/>
+              <bgColor theme="4" tint="0.59999389629810485"/>
+            </patternFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FF999999"/>
+            </left>
+            <right style="thin">
+              <color rgb="FF999999"/>
+            </right>
+            <top style="thin">
+              <color rgb="FF999999"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FF999999"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF828282"/>
+          </font>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor rgb="FFFFFFFF"/>
+              <bgColor rgb="FFFFFFFF"/>
+            </patternFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FFE0E0E0"/>
+            </left>
+            <right style="thin">
+              <color rgb="FFE0E0E0"/>
+            </right>
+            <top style="thin">
+              <color rgb="FFE0E0E0"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FFE0E0E0"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF000000"/>
+          </font>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor rgb="FFFFFFFF"/>
+              <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+            </patternFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FFCCCCCC"/>
+            </left>
+            <right style="thin">
+              <color rgb="FFCCCCCC"/>
+            </right>
+            <top style="thin">
+              <color rgb="FFCCCCCC"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FFCCCCCC"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
         <dxf>
           <font>
             <color rgb="FF000000"/>
@@ -3891,6 +4364,234 @@
             <horizontal/>
           </border>
         </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF000000"/>
+          </font>
+          <fill>
+            <gradientFill degree="90">
+              <stop position="0">
+                <color rgb="FFF8E162"/>
+              </stop>
+              <stop position="1">
+                <color rgb="FFFCF7E0"/>
+              </stop>
+            </gradientFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FF999999"/>
+            </left>
+            <right style="thin">
+              <color rgb="FF999999"/>
+            </right>
+            <top style="thin">
+              <color rgb="FF999999"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FF999999"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF000000"/>
+          </font>
+          <fill>
+            <gradientFill degree="90">
+              <stop position="0">
+                <color rgb="FFF8E162"/>
+              </stop>
+              <stop position="1">
+                <color rgb="FFFCF7E0"/>
+              </stop>
+            </gradientFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FF999999"/>
+            </left>
+            <right style="thin">
+              <color rgb="FF999999"/>
+            </right>
+            <top style="thin">
+              <color rgb="FF999999"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FF999999"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF000000"/>
+          </font>
+          <fill>
+            <gradientFill degree="90">
+              <stop position="0">
+                <color rgb="FFF8E162"/>
+              </stop>
+              <stop position="1">
+                <color rgb="FFFCF7E0"/>
+              </stop>
+            </gradientFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FF999999"/>
+            </left>
+            <right style="thin">
+              <color rgb="FF999999"/>
+            </right>
+            <top style="thin">
+              <color rgb="FF999999"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FF999999"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF000000"/>
+          </font>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor auto="1"/>
+              <bgColor rgb="FFFFC000"/>
+            </patternFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FF999999"/>
+            </left>
+            <right style="thin">
+              <color rgb="FF999999"/>
+            </right>
+            <top style="thin">
+              <color rgb="FF999999"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FF999999"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF828282"/>
+          </font>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor theme="4" tint="0.79998168889431442"/>
+              <bgColor theme="4" tint="0.79998168889431442"/>
+            </patternFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FFCCCCCC"/>
+            </left>
+            <right style="thin">
+              <color rgb="FFCCCCCC"/>
+            </right>
+            <top style="thin">
+              <color rgb="FFCCCCCC"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FFCCCCCC"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF000000"/>
+          </font>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor theme="4" tint="0.59999389629810485"/>
+              <bgColor theme="4" tint="0.59999389629810485"/>
+            </patternFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FF999999"/>
+            </left>
+            <right style="thin">
+              <color rgb="FF999999"/>
+            </right>
+            <top style="thin">
+              <color rgb="FF999999"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FF999999"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF828282"/>
+          </font>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor rgb="FFFFFFFF"/>
+              <bgColor rgb="FFFFFFFF"/>
+            </patternFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FFE0E0E0"/>
+            </left>
+            <right style="thin">
+              <color rgb="FFE0E0E0"/>
+            </right>
+            <top style="thin">
+              <color rgb="FFE0E0E0"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FFE0E0E0"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF000000"/>
+          </font>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor rgb="FFFFFFFF"/>
+              <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+            </patternFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FFCCCCCC"/>
+            </left>
+            <right style="thin">
+              <color rgb="FFCCCCCC"/>
+            </right>
+            <top style="thin">
+              <color rgb="FFCCCCCC"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FFCCCCCC"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
       </x14:dxfs>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -3909,21 +4610,123 @@
         </x14:slicerStyle>
         <x14:slicerStyle name="Goat Slicer 2 2">
           <x14:slicerStyleElements>
-            <x14:slicerStyleElement type="unselectedItemWithData" dxfId="15"/>
-            <x14:slicerStyleElement type="unselectedItemWithNoData" dxfId="14"/>
-            <x14:slicerStyleElement type="selectedItemWithData" dxfId="13"/>
-            <x14:slicerStyleElement type="selectedItemWithNoData" dxfId="12"/>
-            <x14:slicerStyleElement type="hoveredUnselectedItemWithData" dxfId="11"/>
-            <x14:slicerStyleElement type="hoveredSelectedItemWithData" dxfId="10"/>
-            <x14:slicerStyleElement type="hoveredUnselectedItemWithNoData" dxfId="9"/>
-            <x14:slicerStyleElement type="hoveredSelectedItemWithNoData" dxfId="8"/>
+            <x14:slicerStyleElement type="unselectedItemWithData" dxfId="31"/>
+            <x14:slicerStyleElement type="unselectedItemWithNoData" dxfId="30"/>
+            <x14:slicerStyleElement type="selectedItemWithData" dxfId="29"/>
+            <x14:slicerStyleElement type="selectedItemWithNoData" dxfId="28"/>
+            <x14:slicerStyleElement type="hoveredUnselectedItemWithData" dxfId="27"/>
+            <x14:slicerStyleElement type="hoveredSelectedItemWithData" dxfId="26"/>
+            <x14:slicerStyleElement type="hoveredUnselectedItemWithNoData" dxfId="25"/>
+            <x14:slicerStyleElement type="hoveredSelectedItemWithNoData" dxfId="24"/>
           </x14:slicerStyleElements>
         </x14:slicerStyle>
         <x14:slicerStyle name="Slicer Style 1"/>
       </x14:slicerStyles>
     </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{A0A4C193-F2C1-4fcb-8827-314CF55A85BB}">
-      <x15:dxfs count="7">
+      <x15:dxfs count="14">
+        <dxf>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor theme="4" tint="0.39985351115451523"/>
+              <bgColor rgb="FF92D050"/>
+            </patternFill>
+          </fill>
+          <border>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <fill>
+            <gradientFill degree="90">
+              <stop position="0">
+                <color theme="0" tint="-0.14999847407452621"/>
+              </stop>
+              <stop position="1">
+                <color theme="0" tint="-0.14999847407452621"/>
+              </stop>
+            </gradientFill>
+          </fill>
+          <border>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor theme="2" tint="-0.499984740745262"/>
+              <bgColor rgb="FF002060"/>
+            </patternFill>
+          </fill>
+          <border>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <b/>
+            <i val="0"/>
+            <sz val="20"/>
+            <color theme="5" tint="0.39994506668294322"/>
+          </font>
+          <border>
+            <left/>
+            <right/>
+            <top/>
+            <bottom/>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <b/>
+            <i val="0"/>
+            <sz val="24"/>
+            <color theme="7" tint="0.39991454817346722"/>
+          </font>
+          <border>
+            <left/>
+            <right/>
+            <top/>
+            <bottom/>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <b/>
+            <i val="0"/>
+            <sz val="22"/>
+            <color theme="7" tint="0.59996337778862885"/>
+          </font>
+          <border>
+            <left/>
+            <right/>
+            <top/>
+            <bottom/>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <sz val="24"/>
+            <color theme="2"/>
+          </font>
+          <border>
+            <left/>
+            <right/>
+            <top/>
+            <bottom/>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
         <dxf>
           <fill>
             <patternFill patternType="solid">
@@ -15525,8 +16328,8 @@
       <xdr:row>29</xdr:row>
       <xdr:rowOff>95249</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="53" name="Department">
@@ -15549,7 +16352,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -15603,8 +16406,8 @@
       <xdr:row>41</xdr:row>
       <xdr:rowOff>114301</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="54" name="Working status">
@@ -15627,7 +16430,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -15681,8 +16484,8 @@
       <xdr:row>70</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="55" name="Employee Category">
@@ -15705,7 +16508,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -15759,8 +16562,8 @@
       <xdr:row>54</xdr:row>
       <xdr:rowOff>97155</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="56" name="Employee Type">
@@ -15783,7 +16586,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -15833,7 +16636,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>38</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
+      <xdr:colOff>152400</xdr:colOff>
       <xdr:row>92</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
@@ -15851,7 +16654,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14954250" y="12630150"/>
-          <a:ext cx="8515350" cy="5010150"/>
+          <a:ext cx="8362950" cy="5010150"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -15898,9 +16701,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>38</xdr:col>
-      <xdr:colOff>285750</xdr:colOff>
+      <xdr:colOff>171450</xdr:colOff>
       <xdr:row>92</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -15940,8 +16743,8 @@
       <xdr:row>12</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer" Requires="tsle">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer">
+      <mc:Choice Requires="tsle">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="7" name="Date of confirmation">
@@ -15959,12 +16762,12 @@
           </xdr:xfrm>
           <a:graphic>
             <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2012/timeslicer">
-              <tsle:timeslicer xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer" name="Date of confirmation"/>
+              <tsle:timeslicer name="Date of confirmation"/>
             </a:graphicData>
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -16017,8 +16820,8 @@
       <xdr:row>92</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer" Requires="tsle">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer">
+      <mc:Choice Requires="tsle">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="11" name="Date of Join">
@@ -16036,12 +16839,12 @@
           </xdr:xfrm>
           <a:graphic>
             <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2012/timeslicer">
-              <tsle:timeslicer xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer" name="Date of Join"/>
+              <tsle:timeslicer name="Date of Join"/>
             </a:graphicData>
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -33439,7 +34242,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8F383169-DCAD-4C02-8CAF-48B0FFF91D1C}" name="Department Split" cacheId="58" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8F383169-DCAD-4C02-8CAF-48B0FFF91D1C}" name="Department Split" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
   <location ref="D3:E11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
     <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" sortType="ascending" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -33560,42 +34363,15 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4BB8B950-CBA3-4475-9DB2-E746E2597820}" name="Confirmation Pipeline" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
-  <location ref="H3:I7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{80C3D2EF-384B-4133-9FF5-432422FEDAB3}" name="​Hiring Trends" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+  <location ref="A3:B16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="18">
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="9">
-        <item x="1"/>
-        <item x="6"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="5"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
     <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="67">
@@ -33675,21 +34451,50 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0" defaultSubtotal="0"/>
-    <pivotField showAll="0" defaultSubtotal="0"/>
-    <pivotField showAll="0" defaultSubtotal="0">
-      <items count="4">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="15">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
         <item x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item t="default"/>
       </items>
     </pivotField>
   </pivotFields>
   <rowFields count="1">
-    <field x="5"/>
+    <field x="15"/>
   </rowFields>
-  <rowItems count="4">
+  <rowItems count="13">
     <i>
       <x/>
     </i>
@@ -33698,6 +34503,33 @@
     </i>
     <i>
       <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
     </i>
     <i t="grand">
       <x/>
@@ -33709,7 +34541,7 @@
   <dataFields count="1">
     <dataField name="Count of ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="9">
+  <chartFormats count="2">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -33719,92 +34551,11 @@
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="7" format="1" series="1">
+    <chartFormat chart="6" format="2" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="7" format="2">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="5" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="7" format="3">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="5" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="7" format="4">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="5" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="5" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="6">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="5" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="7">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="5" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="8">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="5" count="1" selected="0">
-            <x v="2"/>
           </reference>
         </references>
       </pivotArea>
@@ -33823,6 +34574,378 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1ECB7C01-64F5-4AC5-9A2A-F5FB42232C19}" name="Marital Status &amp; Health" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="L3:M26" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="18">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="67">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="35"/>
+        <item x="34"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="11">
+        <item x="6"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="9"/>
+    <field x="10"/>
+  </rowFields>
+  <rowItems count="23">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="6"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
+    </i>
+    <i r="1">
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="6"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
+    </i>
+    <i r="1">
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="9"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{99A570F6-77D8-4071-95E0-C685B2BA29D7}" name="​Commute Analysis" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="H3:I11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="18">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="67">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="35"/>
+        <item x="34"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="8">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="12"/>
+  </rowFields>
+  <rowItems count="8">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6873C426-90CA-46C5-BFBD-92FABBF147D9}" name="​Gender Diversity" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:E13" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="18">
@@ -34005,7 +35128,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BFB609F8-3DD5-4FA1-B2ED-A8E7D95564D2}" name="Gender Distribution" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
   <location ref="P3:Q7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="18">
@@ -34219,378 +35342,6 @@
       </pivotArea>
     </chartFormat>
   </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1ECB7C01-64F5-4AC5-9A2A-F5FB42232C19}" name="Marital Status &amp; Health" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="L3:M26" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="18">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="67">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="35"/>
-        <item x="34"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item x="65"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="11">
-        <item x="6"/>
-        <item x="1"/>
-        <item x="8"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item x="0"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="9"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0" defaultSubtotal="0"/>
-    <pivotField showAll="0" defaultSubtotal="0"/>
-    <pivotField showAll="0" defaultSubtotal="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="9"/>
-    <field x="10"/>
-  </rowFields>
-  <rowItems count="23">
-    <i>
-      <x/>
-    </i>
-    <i r="1">
-      <x/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x v="2"/>
-    </i>
-    <i r="1">
-      <x v="3"/>
-    </i>
-    <i r="1">
-      <x v="4"/>
-    </i>
-    <i r="1">
-      <x v="5"/>
-    </i>
-    <i r="1">
-      <x v="6"/>
-    </i>
-    <i r="1">
-      <x v="7"/>
-    </i>
-    <i r="1">
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x v="2"/>
-    </i>
-    <i r="1">
-      <x v="3"/>
-    </i>
-    <i r="1">
-      <x v="4"/>
-    </i>
-    <i r="1">
-      <x v="5"/>
-    </i>
-    <i r="1">
-      <x v="6"/>
-    </i>
-    <i r="1">
-      <x v="7"/>
-    </i>
-    <i r="1">
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i r="1">
-      <x v="9"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{99A570F6-77D8-4071-95E0-C685B2BA29D7}" name="​Commute Analysis" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="H3:I11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="18">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="67">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="35"/>
-        <item x="34"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item x="65"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="8">
-        <item x="3"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0" defaultSubtotal="0"/>
-    <pivotField showAll="0" defaultSubtotal="0"/>
-    <pivotField showAll="0" defaultSubtotal="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="12"/>
-  </rowFields>
-  <rowItems count="8">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -34991,378 +35742,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F1A1C601-2590-4257-9CD5-1BAF090DD9BA}" name="Average Salary" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="D3:E12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="18">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="9">
-        <item x="1"/>
-        <item x="6"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="5"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="67">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="35"/>
-        <item x="34"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item x="65"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="9">
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Average of Salary" fld="14" subtotal="average" baseField="2" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4DCCFBC5-6225-4DC7-B59E-6245A2066D91}" name="​Salary vs. Employee Type" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="J3:K7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="18">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="67">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="35"/>
-        <item x="34"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item x="65"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="5"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Average of Salary" fld="14" subtotal="average" baseField="5" baseItem="1"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DE333CB7-180B-430F-BFC5-B9C56E35AD8B}" name="Salary by Designation" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DE333CB7-180B-430F-BFC5-B9C56E35AD8B}" name="Salary by Designation" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
   <location ref="G3:H15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="18">
     <pivotField showAll="0"/>
@@ -35592,8 +35972,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1A4DE049-25EA-4EDA-9C5F-C54D65036232}" name="Monthly payroll" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1A4DE049-25EA-4EDA-9C5F-C54D65036232}" name="Monthly payroll" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
   <location ref="A3:B12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="18">
     <pivotField showAll="0"/>
@@ -35812,7 +36192,641 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F1A1C601-2590-4257-9CD5-1BAF090DD9BA}" name="Average Salary" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="D3:E12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="18">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="9">
+        <item x="1"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="67">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="35"/>
+        <item x="34"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="9">
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Salary" fld="14" subtotal="average" baseField="2" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4DCCFBC5-6225-4DC7-B59E-6245A2066D91}" name="​Salary vs. Employee Type" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="J3:K7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="18">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="67">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="35"/>
+        <item x="34"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Salary" fld="14" subtotal="average" baseField="5" baseItem="1"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4BB8B950-CBA3-4475-9DB2-E746E2597820}" name="Confirmation Pipeline" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
+  <location ref="H3:I7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="18">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="9">
+        <item x="1"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="67">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="35"/>
+        <item x="34"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="9">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="7" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="7" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="7" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="7" format="4">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="6">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="7">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="8">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3F48149E-3120-4942-AE51-EE0B59AF380A}" name="Employee Status" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="D3:F8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="18">
@@ -35955,217 +36969,6 @@
     <dataField name="Count of ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
     <dataField name="Count of Working status" fld="13" subtotal="count" showDataAs="percentOfTotal" baseField="0" baseItem="0" numFmtId="10"/>
   </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{80C3D2EF-384B-4133-9FF5-432422FEDAB3}" name="​Hiring Trends" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
-  <location ref="A3:B16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="18">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="67">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="35"/>
-        <item x="34"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item x="65"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="15">
-        <item sd="0" x="0"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="2"/>
-        <item sd="0" x="3"/>
-        <item sd="0" x="4"/>
-        <item sd="0" x="5"/>
-        <item sd="0" x="6"/>
-        <item sd="0" x="7"/>
-        <item sd="0" x="8"/>
-        <item sd="0" x="9"/>
-        <item sd="0" x="10"/>
-        <item sd="0" x="11"/>
-        <item sd="0" x="12"/>
-        <item sd="0" x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item sd="0" x="4"/>
-        <item sd="0" x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="2"/>
-        <item sd="0" x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="15"/>
-  </rowFields>
-  <rowItems count="13">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="2">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
